--- a/data/survey_data.xlsx
+++ b/data/survey_data.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <x:si>
     <x:t xml:space="preserve">ID</x:t>
   </x:si>
@@ -70,6 +70,27 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Scale</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">A strategic thriller</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"Don't Stop Believin'" - Journey</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No idea </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Outcomes</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">A clever documentary</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"Happy" - Pharrell Williams</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Dkdls</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -166,8 +187,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J2" insertRow="1" totalsRowShown="0">
-  <x:autoFilter ref="A1:J2"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J4" insertRow="1" totalsRowShown="0">
+  <x:autoFilter ref="A1:J4"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" uniqueName="1" name="ID" dataDxfId="0"/>
     <x:tableColumn id="2" uniqueName="2" name="Start time" dataDxfId="3"/>
@@ -556,11 +577,67 @@
         <x:v>14</x:v>
       </x:c>
     </x:row>
+    <x:row r="3" hidden="0">
+      <x:c r="A3">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="2">
+        <x:v>46099.4307638889</x:v>
+      </x:c>
+      <x:c r="C3" s="2">
+        <x:v>46099.4314699074</x:v>
+      </x:c>
+      <x:c r="D3" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="2"/>
+      <x:c r="G3" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H3" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I3" s="10" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J3" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" hidden="0">
+      <x:c r="A4">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="2">
+        <x:v>46099.4319560185</x:v>
+      </x:c>
+      <x:c r="C4" s="2">
+        <x:v>46099.4321643518</x:v>
+      </x:c>
+      <x:c r="D4" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E4" s="10" t="s"/>
+      <x:c r="F4" s="2"/>
+      <x:c r="G4" s="10" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H4" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I4" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J4" s="10" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="Ra256bdaf56f74d56"/>
+    <x:tablePart r:id="R36d516b826b1498d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/survey_data.xlsx
+++ b/data/survey_data.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <x:si>
     <x:t xml:space="preserve">ID</x:t>
   </x:si>
@@ -69,28 +69,43 @@
     <x:t xml:space="preserve">"Smooth Operator" - Sade</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Scale</x:t>
+    <x:t xml:space="preserve">Scalatronix </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Knowledge</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">A fast-paced political drama</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"Don't Stop Believin'" - Journey</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">NOT The Flatliners</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Bridgers</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">A strategic thriller</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">"Don't Stop Believin'" - Journey</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No idea </x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Outcomes</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">A clever documentary</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">"Happy" - Pharrell Williams</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Dkdls</x:t>
+    <x:t xml:space="preserve">"We Are the Champtions" - Queen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Hamnet</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No is not the answer</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Fantastic 4 (with the MDCKO) </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"I will survive!" - Gloria Gaynor</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Wonderkids </x:t>
   </x:si>
 </x:sst>
 </file>
@@ -187,8 +202,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J4" insertRow="1" totalsRowShown="0">
-  <x:autoFilter ref="A1:J4"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J8" insertRow="1" totalsRowShown="0">
+  <x:autoFilter ref="A1:J8"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" uniqueName="1" name="ID" dataDxfId="0"/>
     <x:tableColumn id="2" uniqueName="2" name="Start time" dataDxfId="3"/>
@@ -551,13 +566,13 @@
     </x:row>
     <x:row r="2" hidden="0">
       <x:c r="A2">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B2" s="2">
-        <x:v>46099.2735763889</x:v>
+        <x:v>46099.5521296296</x:v>
       </x:c>
       <x:c r="C2" s="2">
-        <x:v>46099.2749305556</x:v>
+        <x:v>46099.5524652778</x:v>
       </x:c>
       <x:c r="D2" s="10" t="s">
         <x:v>10</x:v>
@@ -579,13 +594,13 @@
     </x:row>
     <x:row r="3" hidden="0">
       <x:c r="A3">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B3" s="2">
-        <x:v>46099.4307638889</x:v>
+        <x:v>46099.5519444444</x:v>
       </x:c>
       <x:c r="C3" s="2">
-        <x:v>46099.4314699074</x:v>
+        <x:v>46099.552662037</x:v>
       </x:c>
       <x:c r="D3" s="10" t="s">
         <x:v>10</x:v>
@@ -593,27 +608,27 @@
       <x:c r="E3" s="10" t="s"/>
       <x:c r="F3" s="2"/>
       <x:c r="G3" s="10" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H3" s="10" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="I3" s="10" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J3" s="10" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="4" hidden="0">
       <x:c r="A4">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B4" s="2">
-        <x:v>46099.4319560185</x:v>
+        <x:v>46099.5519907407</x:v>
       </x:c>
       <x:c r="C4" s="2">
-        <x:v>46099.4321643518</x:v>
+        <x:v>46099.5526967593</x:v>
       </x:c>
       <x:c r="D4" s="10" t="s">
         <x:v>10</x:v>
@@ -621,23 +636,135 @@
       <x:c r="E4" s="10" t="s"/>
       <x:c r="F4" s="2"/>
       <x:c r="G4" s="10" t="s">
-        <x:v>18</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H4" s="10" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I4" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J4" s="10" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="I4" s="10" t="s">
+    </x:row>
+    <x:row r="5" hidden="0">
+      <x:c r="A5">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B5" s="2">
+        <x:v>46099.5521759259</x:v>
+      </x:c>
+      <x:c r="C5" s="2">
+        <x:v>46099.5527199074</x:v>
+      </x:c>
+      <x:c r="D5" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="2"/>
+      <x:c r="G5" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H5" s="10" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="J4" s="10" t="s">
+      <x:c r="I5" s="10" t="s">
         <x:v>21</x:v>
+      </x:c>
+      <x:c r="J5" s="10" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" hidden="0">
+      <x:c r="A6">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B6" s="2">
+        <x:v>46099.5521064815</x:v>
+      </x:c>
+      <x:c r="C6" s="2">
+        <x:v>46099.5527546296</x:v>
+      </x:c>
+      <x:c r="D6" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E6" s="10" t="s"/>
+      <x:c r="F6" s="2"/>
+      <x:c r="G6" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H6" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I6" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J6" s="10" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" hidden="0">
+      <x:c r="A7">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B7" s="2">
+        <x:v>46099.5519907407</x:v>
+      </x:c>
+      <x:c r="C7" s="2">
+        <x:v>46099.5527893519</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s"/>
+      <x:c r="F7" s="2"/>
+      <x:c r="G7" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" hidden="0">
+      <x:c r="A8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B8" s="2">
+        <x:v>46099.552349537</x:v>
+      </x:c>
+      <x:c r="C8" s="2">
+        <x:v>46099.5527893519</x:v>
+      </x:c>
+      <x:c r="D8" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E8" s="10" t="s"/>
+      <x:c r="F8" s="2"/>
+      <x:c r="G8" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H8" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I8" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="J8" s="10" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="R36d516b826b1498d"/>
+    <x:tablePart r:id="R9776e91809254ede"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/survey_data.xlsx
+++ b/data/survey_data.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <x:si>
     <x:t xml:space="preserve">ID</x:t>
   </x:si>
@@ -106,6 +106,54 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Wonderkids </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Intelligence</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Invincables</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The Unbelieved</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Connectors</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The Supertransformers</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Outcomes</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The mighty trio</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ACT</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PowerBankers</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Horizontals</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Omnipotent 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The Unstoppable Horizons </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The Incredibles</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The Invincibles </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The Impossibles</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Hit don’t miss</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -202,8 +250,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J8" insertRow="1" totalsRowShown="0">
-  <x:autoFilter ref="A1:J8"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J23" insertRow="1" totalsRowShown="0">
+  <x:autoFilter ref="A1:J23"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" uniqueName="1" name="ID" dataDxfId="0"/>
     <x:tableColumn id="2" uniqueName="2" name="Start time" dataDxfId="3"/>
@@ -760,11 +808,431 @@
         <x:v>26</x:v>
       </x:c>
     </x:row>
+    <x:row r="9" hidden="0">
+      <x:c r="A9">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B9" s="2">
+        <x:v>46099.5521412037</x:v>
+      </x:c>
+      <x:c r="C9" s="2">
+        <x:v>46099.5528125</x:v>
+      </x:c>
+      <x:c r="D9" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E9" s="10" t="s"/>
+      <x:c r="F9" s="2"/>
+      <x:c r="G9" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H9" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I9" s="10" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J9" s="10" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" hidden="0">
+      <x:c r="A10">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B10" s="2">
+        <x:v>46099.5520949074</x:v>
+      </x:c>
+      <x:c r="C10" s="2">
+        <x:v>46099.5528240741</x:v>
+      </x:c>
+      <x:c r="D10" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E10" s="10" t="s"/>
+      <x:c r="F10" s="2"/>
+      <x:c r="G10" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H10" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I10" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J10" s="10" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" hidden="0">
+      <x:c r="A11">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B11" s="2">
+        <x:v>46099.5520949074</x:v>
+      </x:c>
+      <x:c r="C11" s="2">
+        <x:v>46099.5528472222</x:v>
+      </x:c>
+      <x:c r="D11" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E11" s="10" t="s"/>
+      <x:c r="F11" s="2"/>
+      <x:c r="G11" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H11" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I11" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J11" s="10" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" hidden="0">
+      <x:c r="A12">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B12" s="2">
+        <x:v>46099.5521412037</x:v>
+      </x:c>
+      <x:c r="C12" s="2">
+        <x:v>46099.5528935185</x:v>
+      </x:c>
+      <x:c r="D12" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E12" s="10" t="s"/>
+      <x:c r="F12" s="2"/>
+      <x:c r="G12" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H12" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I12" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J12" s="10" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" hidden="0">
+      <x:c r="A13">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B13" s="2">
+        <x:v>46099.5521296296</x:v>
+      </x:c>
+      <x:c r="C13" s="2">
+        <x:v>46099.5529050926</x:v>
+      </x:c>
+      <x:c r="D13" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E13" s="10" t="s"/>
+      <x:c r="F13" s="2"/>
+      <x:c r="G13" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H13" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I13" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="J13" s="10" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" hidden="0">
+      <x:c r="A14">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B14" s="2">
+        <x:v>46099.5521527778</x:v>
+      </x:c>
+      <x:c r="C14" s="2">
+        <x:v>46099.5529282407</x:v>
+      </x:c>
+      <x:c r="D14" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E14" s="10" t="s"/>
+      <x:c r="F14" s="2"/>
+      <x:c r="G14" s="10" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H14" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I14" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J14" s="10" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" hidden="0">
+      <x:c r="A15">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B15" s="2">
+        <x:v>46099.5522222222</x:v>
+      </x:c>
+      <x:c r="C15" s="2">
+        <x:v>46099.552962963</x:v>
+      </x:c>
+      <x:c r="D15" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E15" s="10" t="s"/>
+      <x:c r="F15" s="2"/>
+      <x:c r="G15" s="10" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H15" s="10" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I15" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="J15" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" hidden="0">
+      <x:c r="A16">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B16" s="2">
+        <x:v>46099.5520949074</x:v>
+      </x:c>
+      <x:c r="C16" s="2">
+        <x:v>46099.5529976852</x:v>
+      </x:c>
+      <x:c r="D16" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E16" s="10" t="s"/>
+      <x:c r="F16" s="2"/>
+      <x:c r="G16" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H16" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I16" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J16" s="10" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" hidden="0">
+      <x:c r="A17">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B17" s="2">
+        <x:v>46099.5521527778</x:v>
+      </x:c>
+      <x:c r="C17" s="2">
+        <x:v>46099.5530208333</x:v>
+      </x:c>
+      <x:c r="D17" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E17" s="10" t="s"/>
+      <x:c r="F17" s="2"/>
+      <x:c r="G17" s="10" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H17" s="10" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I17" s="10" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J17" s="10" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" hidden="0">
+      <x:c r="A18">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B18" s="2">
+        <x:v>46099.5519907407</x:v>
+      </x:c>
+      <x:c r="C18" s="2">
+        <x:v>46099.5531828704</x:v>
+      </x:c>
+      <x:c r="D18" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E18" s="10" t="s"/>
+      <x:c r="F18" s="2"/>
+      <x:c r="G18" s="10" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H18" s="10" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I18" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="J18" s="10" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" hidden="0">
+      <x:c r="A19">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B19" s="2">
+        <x:v>46099.5520601852</x:v>
+      </x:c>
+      <x:c r="C19" s="2">
+        <x:v>46099.5532175926</x:v>
+      </x:c>
+      <x:c r="D19" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E19" s="10" t="s"/>
+      <x:c r="F19" s="2"/>
+      <x:c r="G19" s="10" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H19" s="10" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I19" s="10" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J19" s="10" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" hidden="0">
+      <x:c r="A20">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B20" s="2">
+        <x:v>46099.5521875</x:v>
+      </x:c>
+      <x:c r="C20" s="2">
+        <x:v>46099.5532175926</x:v>
+      </x:c>
+      <x:c r="D20" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E20" s="10" t="s"/>
+      <x:c r="F20" s="2"/>
+      <x:c r="G20" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H20" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I20" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="J20" s="10" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" hidden="0">
+      <x:c r="A21">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B21" s="2">
+        <x:v>46099.5521064815</x:v>
+      </x:c>
+      <x:c r="C21" s="2">
+        <x:v>46099.5532523148</x:v>
+      </x:c>
+      <x:c r="D21" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E21" s="10" t="s"/>
+      <x:c r="F21" s="2"/>
+      <x:c r="G21" s="10" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H21" s="10" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I21" s="10" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J21" s="10" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" hidden="0">
+      <x:c r="A22">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B22" s="2">
+        <x:v>46099.552025463</x:v>
+      </x:c>
+      <x:c r="C22" s="2">
+        <x:v>46099.553287037</x:v>
+      </x:c>
+      <x:c r="D22" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E22" s="10" t="s"/>
+      <x:c r="F22" s="2"/>
+      <x:c r="G22" s="10" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H22" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I22" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="J22" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" hidden="0">
+      <x:c r="A23">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B23" s="2">
+        <x:v>46099.5521064815</x:v>
+      </x:c>
+      <x:c r="C23" s="2">
+        <x:v>46099.5534027778</x:v>
+      </x:c>
+      <x:c r="D23" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E23" s="10" t="s"/>
+      <x:c r="F23" s="2"/>
+      <x:c r="G23" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H23" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I23" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J23" s="10" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="R9776e91809254ede"/>
+    <x:tablePart r:id="R80fb2358b9444daf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/survey_data.xlsx
+++ b/data/survey_data.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <x:si>
     <x:t xml:space="preserve">ID</x:t>
   </x:si>
@@ -154,6 +154,75 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Hit don’t miss</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"Happy" - Pharrell Williams</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The Impact Avengers</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">horizontallers</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Outcome Oracle</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Team Horizontal: KB Police (TM)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Fantastic Three</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Zoo Crew :) </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The Super HHHs!</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Captain Planet</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Horizon-stars</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">A clever documentary</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The Rockstars</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The Magnificent Team</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">One-WBG crusaders</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">?</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Koi (fish) - knowledge, outcomes, and innovation. Wise, placid, and reflective :)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The Impact Collective </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">A feel-good comedy</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Spider People </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Wonder Horizontal</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Horizontal Avengers</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Adventurers of the Knowledge Bank</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Super Triangulator</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -250,8 +319,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J23" insertRow="1" totalsRowShown="0">
-  <x:autoFilter ref="A1:J23"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J43" insertRow="1" totalsRowShown="0">
+  <x:autoFilter ref="A1:J43"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" uniqueName="1" name="ID" dataDxfId="0"/>
     <x:tableColumn id="2" uniqueName="2" name="Start time" dataDxfId="3"/>
@@ -1228,11 +1297,571 @@
         <x:v>42</x:v>
       </x:c>
     </x:row>
+    <x:row r="24" hidden="0">
+      <x:c r="A24">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B24" s="2">
+        <x:v>46099.5520833333</x:v>
+      </x:c>
+      <x:c r="C24" s="2">
+        <x:v>46099.5534259259</x:v>
+      </x:c>
+      <x:c r="D24" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E24" s="10" t="s"/>
+      <x:c r="F24" s="2"/>
+      <x:c r="G24" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H24" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I24" s="10" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="J24" s="10" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" hidden="0">
+      <x:c r="A25">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B25" s="2">
+        <x:v>46099.5523842593</x:v>
+      </x:c>
+      <x:c r="C25" s="2">
+        <x:v>46099.5534606481</x:v>
+      </x:c>
+      <x:c r="D25" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E25" s="10" t="s"/>
+      <x:c r="F25" s="2"/>
+      <x:c r="G25" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H25" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I25" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J25" s="10" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" hidden="0">
+      <x:c r="A26">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B26" s="2">
+        <x:v>46099.5519791667</x:v>
+      </x:c>
+      <x:c r="C26" s="2">
+        <x:v>46099.5534606481</x:v>
+      </x:c>
+      <x:c r="D26" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E26" s="10" t="s"/>
+      <x:c r="F26" s="2"/>
+      <x:c r="G26" s="10" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H26" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I26" s="10" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J26" s="10" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" hidden="0">
+      <x:c r="A27">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B27" s="2">
+        <x:v>46099.5520601852</x:v>
+      </x:c>
+      <x:c r="C27" s="2">
+        <x:v>46099.5534606481</x:v>
+      </x:c>
+      <x:c r="D27" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E27" s="10" t="s"/>
+      <x:c r="F27" s="2"/>
+      <x:c r="G27" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H27" s="10" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I27" s="10" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J27" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" hidden="0">
+      <x:c r="A28">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B28" s="2">
+        <x:v>46099.5521296296</x:v>
+      </x:c>
+      <x:c r="C28" s="2">
+        <x:v>46099.5534953704</x:v>
+      </x:c>
+      <x:c r="D28" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E28" s="10" t="s"/>
+      <x:c r="F28" s="2"/>
+      <x:c r="G28" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H28" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I28" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J28" s="10" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" hidden="0">
+      <x:c r="A29">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B29" s="2">
+        <x:v>46099.5521759259</x:v>
+      </x:c>
+      <x:c r="C29" s="2">
+        <x:v>46099.5534953704</x:v>
+      </x:c>
+      <x:c r="D29" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E29" s="10" t="s"/>
+      <x:c r="F29" s="2"/>
+      <x:c r="G29" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H29" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I29" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J29" s="10" t="s">
+        <x:v>49</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" hidden="0">
+      <x:c r="A30">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B30" s="2">
+        <x:v>46099.5522569444</x:v>
+      </x:c>
+      <x:c r="C30" s="2">
+        <x:v>46099.5535185185</x:v>
+      </x:c>
+      <x:c r="D30" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E30" s="10" t="s"/>
+      <x:c r="F30" s="2"/>
+      <x:c r="G30" s="10" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H30" s="10" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I30" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="J30" s="10" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" hidden="0">
+      <x:c r="A31">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B31" s="2">
+        <x:v>46099.5521180556</x:v>
+      </x:c>
+      <x:c r="C31" s="2">
+        <x:v>46099.5535300926</x:v>
+      </x:c>
+      <x:c r="D31" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E31" s="10" t="s"/>
+      <x:c r="F31" s="2"/>
+      <x:c r="G31" s="10" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H31" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I31" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="J31" s="10" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" hidden="0">
+      <x:c r="A32">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B32" s="2">
+        <x:v>46099.552025463</x:v>
+      </x:c>
+      <x:c r="C32" s="2">
+        <x:v>46099.553599537</x:v>
+      </x:c>
+      <x:c r="D32" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E32" s="10" t="s"/>
+      <x:c r="F32" s="2"/>
+      <x:c r="G32" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H32" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I32" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J32" s="10" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" hidden="0">
+      <x:c r="A33">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B33" s="2">
+        <x:v>46099.5520717593</x:v>
+      </x:c>
+      <x:c r="C33" s="2">
+        <x:v>46099.5536574074</x:v>
+      </x:c>
+      <x:c r="D33" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E33" s="10" t="s"/>
+      <x:c r="F33" s="2"/>
+      <x:c r="G33" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H33" s="10" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="I33" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J33" s="10" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" hidden="0">
+      <x:c r="A34">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B34" s="2">
+        <x:v>46099.552025463</x:v>
+      </x:c>
+      <x:c r="C34" s="2">
+        <x:v>46099.5537268519</x:v>
+      </x:c>
+      <x:c r="D34" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E34" s="10" t="s"/>
+      <x:c r="F34" s="2"/>
+      <x:c r="G34" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H34" s="10" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="I34" s="10" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J34" s="10" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" hidden="0">
+      <x:c r="A35">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B35" s="2">
+        <x:v>46099.5525810185</x:v>
+      </x:c>
+      <x:c r="C35" s="2">
+        <x:v>46099.55375</x:v>
+      </x:c>
+      <x:c r="D35" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E35" s="10" t="s"/>
+      <x:c r="F35" s="2"/>
+      <x:c r="G35" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H35" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I35" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J35" s="10" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" hidden="0">
+      <x:c r="A36">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B36" s="2">
+        <x:v>46099.5521643519</x:v>
+      </x:c>
+      <x:c r="C36" s="2">
+        <x:v>46099.5537847222</x:v>
+      </x:c>
+      <x:c r="D36" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E36" s="10" t="s"/>
+      <x:c r="F36" s="2"/>
+      <x:c r="G36" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H36" s="10" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="I36" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J36" s="10" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" hidden="0">
+      <x:c r="A37">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B37" s="2">
+        <x:v>46099.5520601852</x:v>
+      </x:c>
+      <x:c r="C37" s="2">
+        <x:v>46099.5538541667</x:v>
+      </x:c>
+      <x:c r="D37" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E37" s="10" t="s"/>
+      <x:c r="F37" s="2"/>
+      <x:c r="G37" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H37" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I37" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J37" s="10" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" hidden="0">
+      <x:c r="A38">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B38" s="2">
+        <x:v>46099.55375</x:v>
+      </x:c>
+      <x:c r="C38" s="2">
+        <x:v>46099.5539467593</x:v>
+      </x:c>
+      <x:c r="D38" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E38" s="10" t="s"/>
+      <x:c r="F38" s="2"/>
+      <x:c r="G38" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H38" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I38" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="J38" s="10" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" hidden="0">
+      <x:c r="A39">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B39" s="2">
+        <x:v>46099.5521759259</x:v>
+      </x:c>
+      <x:c r="C39" s="2">
+        <x:v>46099.5539930556</x:v>
+      </x:c>
+      <x:c r="D39" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E39" s="10" t="s"/>
+      <x:c r="F39" s="2"/>
+      <x:c r="G39" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H39" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="I39" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J39" s="10" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" hidden="0">
+      <x:c r="A40">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B40" s="2">
+        <x:v>46099.552037037</x:v>
+      </x:c>
+      <x:c r="C40" s="2">
+        <x:v>46099.5540509259</x:v>
+      </x:c>
+      <x:c r="D40" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E40" s="10" t="s"/>
+      <x:c r="F40" s="2"/>
+      <x:c r="G40" s="10" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H40" s="10" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="I40" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J40" s="10" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" hidden="0">
+      <x:c r="A41">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B41" s="2">
+        <x:v>46099.5521064815</x:v>
+      </x:c>
+      <x:c r="C41" s="2">
+        <x:v>46099.5541087963</x:v>
+      </x:c>
+      <x:c r="D41" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E41" s="10" t="s"/>
+      <x:c r="F41" s="2"/>
+      <x:c r="G41" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H41" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I41" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J41" s="10" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" hidden="0">
+      <x:c r="A42">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B42" s="2">
+        <x:v>46099.552025463</x:v>
+      </x:c>
+      <x:c r="C42" s="2">
+        <x:v>46099.5543055556</x:v>
+      </x:c>
+      <x:c r="D42" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E42" s="10" t="s"/>
+      <x:c r="F42" s="2"/>
+      <x:c r="G42" s="10" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H42" s="10" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I42" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J42" s="10" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" hidden="0">
+      <x:c r="A43">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B43" s="2">
+        <x:v>46099.5520717593</x:v>
+      </x:c>
+      <x:c r="C43" s="2">
+        <x:v>46099.5546875</x:v>
+      </x:c>
+      <x:c r="D43" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E43" s="10" t="s"/>
+      <x:c r="F43" s="2"/>
+      <x:c r="G43" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H43" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I43" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J43" s="10" t="s">
+        <x:v>65</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="R80fb2358b9444daf"/>
+    <x:tablePart r:id="Rc566e01903ee4f84"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/survey_data.xlsx
+++ b/data/survey_data.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <x:si>
     <x:t xml:space="preserve">ID</x:t>
   </x:si>
@@ -223,6 +223,12 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Super Triangulator</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The Mission Possible Crew</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Horizons</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -319,8 +325,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J43" insertRow="1" totalsRowShown="0">
-  <x:autoFilter ref="A1:J43"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J45" insertRow="1" totalsRowShown="0">
+  <x:autoFilter ref="A1:J45"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" uniqueName="1" name="ID" dataDxfId="0"/>
     <x:tableColumn id="2" uniqueName="2" name="Start time" dataDxfId="3"/>
@@ -1857,11 +1863,67 @@
         <x:v>65</x:v>
       </x:c>
     </x:row>
+    <x:row r="44" hidden="0">
+      <x:c r="A44">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B44" s="2">
+        <x:v>46099.5520486111</x:v>
+      </x:c>
+      <x:c r="C44" s="2">
+        <x:v>46099.5554166667</x:v>
+      </x:c>
+      <x:c r="D44" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E44" s="10" t="s"/>
+      <x:c r="F44" s="2"/>
+      <x:c r="G44" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H44" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I44" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J44" s="10" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" hidden="0">
+      <x:c r="A45">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B45" s="2">
+        <x:v>46099.5519444444</x:v>
+      </x:c>
+      <x:c r="C45" s="2">
+        <x:v>46099.5560416667</x:v>
+      </x:c>
+      <x:c r="D45" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E45" s="10" t="s"/>
+      <x:c r="F45" s="2"/>
+      <x:c r="G45" s="10" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H45" s="10" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I45" s="10" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J45" s="10" t="s">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="Rc566e01903ee4f84"/>
+    <x:tablePart r:id="R9a902871b4d041c9"/>
   </x:tableParts>
 </x:worksheet>
 </file>